--- a/Output Data Tables/AFAT Outputs/Cost Tables/2021/Administrative_Cost_by_Airline_2021.xlsx
+++ b/Output Data Tables/AFAT Outputs/Cost Tables/2021/Administrative_Cost_by_Airline_2021.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,14 +181,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
     <col min="2" max="2" width="17.7109375" customWidth="true"/>
-    <col min="3" max="3" width="11.140625" customWidth="true"/>
+    <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="19.7109375" customWidth="true"/>
-    <col min="5" max="5" width="11.140625" customWidth="true"/>
+    <col min="5" max="5" width="15.85546875" customWidth="true"/>
     <col min="6" max="6" width="12.5703125" customWidth="true"/>
     <col min="7" max="7" width="11.140625" customWidth="true"/>
     <col min="8" max="8" width="12.5703125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>32291619670</v>
+      </c>
+      <c r="C25" s="0">
+        <v>14567828830</v>
+      </c>
+      <c r="D25" s="0">
+        <v>3659155740</v>
+      </c>
+      <c r="E25" s="0">
+        <v>13917856760</v>
+      </c>
+      <c r="F25" s="0">
+        <v>2359779080</v>
+      </c>
+      <c r="G25" s="0">
+        <v>6733055430</v>
+      </c>
+      <c r="H25" s="0">
+        <v>5664698650</v>
+      </c>
+      <c r="I25" s="0">
+        <v>707435050</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1594121530</v>
+      </c>
+      <c r="K25" s="0">
+        <v>15732690130</v>
+      </c>
+      <c r="L25" s="0">
+        <v>81495550660</v>
+      </c>
+      <c r="M25" s="0">
+        <v>97228240790</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>13186181810</v>
+      </c>
+      <c r="C26" s="0">
+        <v>6237660090</v>
+      </c>
+      <c r="D26" s="0">
+        <v>806583020</v>
+      </c>
+      <c r="E26" s="0">
+        <v>4737351470</v>
+      </c>
+      <c r="F26" s="0">
+        <v>924887960</v>
+      </c>
+      <c r="G26" s="0">
+        <v>2308969690</v>
+      </c>
+      <c r="H26" s="0">
+        <v>2086522440</v>
+      </c>
+      <c r="I26" s="0">
+        <v>195409620</v>
+      </c>
+      <c r="J26" s="0">
+        <v>336508350</v>
+      </c>
+      <c r="K26" s="0">
+        <v>1486594070</v>
+      </c>
+      <c r="L26" s="0">
+        <v>30820075410</v>
+      </c>
+      <c r="M26" s="0">
+        <v>32306669480</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2420764030</v>
+      </c>
+      <c r="C27" s="0">
+        <v>2032392000</v>
+      </c>
+      <c r="D27" s="0">
+        <v>274689780</v>
+      </c>
+      <c r="E27" s="0">
+        <v>1463992910</v>
+      </c>
+      <c r="F27" s="0">
+        <v>299304700</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1018599580</v>
+      </c>
+      <c r="H27" s="0">
+        <v>450402190</v>
+      </c>
+      <c r="I27" s="0">
+        <v>119508790</v>
+      </c>
+      <c r="J27" s="0">
+        <v>261328260</v>
+      </c>
+      <c r="K27" s="0">
+        <v>0</v>
+      </c>
+      <c r="L27" s="0">
+        <v>8340982190</v>
+      </c>
+      <c r="M27" s="0">
+        <v>8340982190</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>4537653020</v>
+      </c>
+      <c r="C28" s="0">
+        <v>112388490</v>
+      </c>
+      <c r="D28" s="0">
+        <v>593381610</v>
+      </c>
+      <c r="E28" s="0">
+        <v>1546882320</v>
+      </c>
+      <c r="F28" s="0">
+        <v>14520710</v>
+      </c>
+      <c r="G28" s="0">
+        <v>1225897070</v>
+      </c>
+      <c r="H28" s="0">
+        <v>565640140</v>
+      </c>
+      <c r="I28" s="0">
+        <v>7737310</v>
+      </c>
+      <c r="J28" s="0">
+        <v>466919660</v>
+      </c>
+      <c r="K28" s="0">
+        <v>3830</v>
+      </c>
+      <c r="L28" s="0">
+        <v>9071021180</v>
+      </c>
+      <c r="M28" s="0">
+        <v>9071025010</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>52436218530</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>22950269410</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>5333810150</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>21666083460</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>3598492450</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>11286521770</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>8767263420</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>1030090770</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>2658877800</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>17219288030</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>129727629440</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>146946917470</v>
       </c>
     </row>
